--- a/inst/extdata/region/2026-08-10/wb_projects_gov_menaap.xlsx
+++ b/inst/extdata/region/2026-08-10/wb_projects_gov_menaap.xlsx
@@ -985,9 +985,11 @@
         <v>54</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H2" s="2"/>
+        <v>2025</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>45798</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>55</v>
       </c>
@@ -1019,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>35</v>
@@ -1067,7 +1069,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
